--- a/inst/extdata/GRAFS_arrows_ids.xlsx
+++ b/inst/extdata/GRAFS_arrows_ids.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pruebasaluuclm-my.sharepoint.com/personal/alfredo_rodriguez_uclm_es/Documents/Drive/git/GRAFS/inst/extdata/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PhD\GRAFS_plot\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB7A3C2D-8364-8841-A257-3F12602506B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6883F41A-8C04-46E8-A999-F0734E513EC3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9360" yWindow="500" windowWidth="29040" windowHeight="15720" xr2:uid="{EDCD53E2-D21F-4CB2-93C7-EB69C032F47B}"/>
   </bookViews>
@@ -20,15 +20,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -39,9 +30,6 @@
     <t>label</t>
   </si>
   <si>
-    <t>&lt;SYF_GRASS&gt;</t>
-  </si>
-  <si>
     <t>q2Cn5xlCuZCPZr2LdWGl-94</t>
   </si>
   <si>
@@ -54,114 +42,48 @@
     <t>q2Cn5xlCuZCPZr2LdWGl-98</t>
   </si>
   <si>
-    <t>&lt;CROP_EXPORT&gt;</t>
-  </si>
-  <si>
-    <t>&lt;IMPORT_ANIMALCR&gt;</t>
-  </si>
-  <si>
     <t>rK_GwhreT1srsj36wAeV-52</t>
   </si>
   <si>
     <t>q2Cn5xlCuZCPZr2LdWGl-90</t>
   </si>
   <si>
-    <t>&lt;LIVESTOCK_TO_GRASS&gt;</t>
-  </si>
-  <si>
-    <t>&lt;LIVESTOCK_TO_CROPS&gt;</t>
-  </si>
-  <si>
     <t>q2Cn5xlCuZCPZr2LdWGl-91</t>
   </si>
   <si>
-    <t>&lt;ORGOT&gt;</t>
-  </si>
-  <si>
     <t>q2Cn5xlCuZCPZr2LdWGl-99</t>
   </si>
   <si>
-    <t>&lt;CROP_SURPLUS&gt;</t>
-  </si>
-  <si>
     <t>q2Cn5xlCuZCPZr2LdWGl-41</t>
   </si>
   <si>
     <t>rK_GwhreT1srsj36wAeV-50</t>
   </si>
   <si>
-    <t>&lt;WASTEWATER&gt;</t>
-  </si>
-  <si>
-    <t>&lt;CROPS_TO_POP&gt;</t>
-  </si>
-  <si>
     <t>q2Cn5xlCuZCPZr2LdWGl-46</t>
   </si>
   <si>
-    <t>&lt;CROPS_TO_LIVESTOCK&gt;</t>
-  </si>
-  <si>
-    <t>&lt;LIVGASLOSS&gt;</t>
-  </si>
-  <si>
-    <t>&lt;UNKMANURE&gt;</t>
-  </si>
-  <si>
     <t>rK_GwhreT1srsj36wAeV-6</t>
   </si>
   <si>
-    <t>&lt;IMANOT&gt;</t>
-  </si>
-  <si>
     <t>rK_GwhreT1srsj36wAeV-44</t>
   </si>
   <si>
-    <t>&lt;AN_LS_OTH&gt;</t>
-  </si>
-  <si>
-    <t>&lt;LVSTCK_NOEDIBLE&gt;</t>
-  </si>
-  <si>
     <t>rK_GwhreT1srsj36wAeV-28</t>
   </si>
   <si>
-    <t>&lt;LIVESTOCK_EXPORTED&gt;</t>
-  </si>
-  <si>
     <t>q2Cn5xlCuZCPZr2LdWGl-100</t>
   </si>
   <si>
-    <t>&lt;LIVESTOCK_TO_HUMAN&gt;</t>
-  </si>
-  <si>
     <t>q2Cn5xlCuZCPZr2LdWGl-92</t>
   </si>
   <si>
     <t>rK_GwhreT1srsj36wAeV-10</t>
   </si>
   <si>
-    <t>&lt;GRASS_TO_LIVESTOCK&gt;</t>
-  </si>
-  <si>
     <t>id</t>
   </si>
   <si>
-    <t>&lt;CRP_LS_OTHUSES&gt;</t>
-  </si>
-  <si>
-    <t>&lt;FIX_DEP_GRASS&gt;</t>
-  </si>
-  <si>
-    <t>&lt;FIX_DEP_CR&gt;</t>
-  </si>
-  <si>
-    <t>&lt;CROP_POPIMPORT&gt;</t>
-  </si>
-  <si>
-    <t>&lt;IMPHMANA&gt;</t>
-  </si>
-  <si>
     <t>nDv0Un9zqEHt-ATpz89Q-1</t>
   </si>
   <si>
@@ -174,87 +96,9 @@
     <t>S4_6scFw5oMBeJrIZRjy-3</t>
   </si>
   <si>
-    <t>&lt;WIDTH_MAX&gt;</t>
-  </si>
-  <si>
-    <t>&lt;SYNTHF_TOTAL&gt;</t>
-  </si>
-  <si>
-    <t>&lt;XSY1&gt;</t>
-  </si>
-  <si>
     <t>labelchange</t>
   </si>
   <si>
-    <t>&lt;XFXC&gt;</t>
-  </si>
-  <si>
-    <t>&lt;XCRSURP&gt;</t>
-  </si>
-  <si>
-    <t>&lt;XCRLOTH&gt;</t>
-  </si>
-  <si>
-    <t>&lt;XCRPOPIMP&gt;</t>
-  </si>
-  <si>
-    <t>&lt;XLVSTOGR&gt;</t>
-  </si>
-  <si>
-    <t>&lt;XLVSTOCR&gt;</t>
-  </si>
-  <si>
-    <t>&lt;XEXPV&gt;</t>
-  </si>
-  <si>
-    <t>&lt;XIMPV&gt;</t>
-  </si>
-  <si>
-    <t>&lt;XWSTWT&gt;</t>
-  </si>
-  <si>
-    <t>&lt;XUNK&gt;</t>
-  </si>
-  <si>
-    <t>&lt;XNLOSS&gt;</t>
-  </si>
-  <si>
-    <t>&lt;XLVSTOHUM&gt;</t>
-  </si>
-  <si>
-    <t>&lt;XLVSTEXP&gt;</t>
-  </si>
-  <si>
-    <t>&lt;XCRPTOPOP&gt;</t>
-  </si>
-  <si>
-    <t>&lt;XORGOT&gt;</t>
-  </si>
-  <si>
-    <t>&lt;XCRPTOLV&gt;</t>
-  </si>
-  <si>
-    <t>&lt;XGRTOLV&gt;</t>
-  </si>
-  <si>
-    <t>&lt;XIMPHUMA&gt;</t>
-  </si>
-  <si>
-    <t>&lt;XLVNOED&gt;</t>
-  </si>
-  <si>
-    <t>&lt;XANOT&gt;</t>
-  </si>
-  <si>
-    <t>&lt;XDEPGR&gt;</t>
-  </si>
-  <si>
-    <t>&lt;XSYGR&gt;</t>
-  </si>
-  <si>
-    <t>&lt;XANLSOT&gt;</t>
-  </si>
-  <si>
     <t>4YDNm8X22fOxdj8KFQc2-1</t>
   </si>
   <si>
@@ -274,6 +118,153 @@
   </si>
   <si>
     <t>q2Cn5xlCuZCPZr2LdWGl-10</t>
+  </si>
+  <si>
+    <t>SYNTHF_TOTAL</t>
+  </si>
+  <si>
+    <t>XSY1</t>
+  </si>
+  <si>
+    <t>SYF_GRASS</t>
+  </si>
+  <si>
+    <t>XSYGR</t>
+  </si>
+  <si>
+    <t>FIX_DEP_GRASS</t>
+  </si>
+  <si>
+    <t>XDEPGR</t>
+  </si>
+  <si>
+    <t>FIX_DEP_CR</t>
+  </si>
+  <si>
+    <t>XFXC</t>
+  </si>
+  <si>
+    <t>CROP_EXPORT</t>
+  </si>
+  <si>
+    <t>XEXPV</t>
+  </si>
+  <si>
+    <t>IMPORT_ANIMALCR</t>
+  </si>
+  <si>
+    <t>XIMPV</t>
+  </si>
+  <si>
+    <t>LIVESTOCK_TO_GRASS</t>
+  </si>
+  <si>
+    <t>XLVSTOGR</t>
+  </si>
+  <si>
+    <t>LIVESTOCK_TO_CROPS</t>
+  </si>
+  <si>
+    <t>XLVSTOCR</t>
+  </si>
+  <si>
+    <t>ORGOT</t>
+  </si>
+  <si>
+    <t>XORGOT</t>
+  </si>
+  <si>
+    <t>CROP_SURPLUS</t>
+  </si>
+  <si>
+    <t>XCRSURP</t>
+  </si>
+  <si>
+    <t>CRP_LS_OTHUSES</t>
+  </si>
+  <si>
+    <t>XCRLOTH</t>
+  </si>
+  <si>
+    <t>WASTEWATER</t>
+  </si>
+  <si>
+    <t>XWSTWT</t>
+  </si>
+  <si>
+    <t>CROPS_TO_POP</t>
+  </si>
+  <si>
+    <t>XCRPTOPOP</t>
+  </si>
+  <si>
+    <t>CROP_POPIMPORT</t>
+  </si>
+  <si>
+    <t>XCRPOPIMP</t>
+  </si>
+  <si>
+    <t>CROPS_TO_LIVESTOCK</t>
+  </si>
+  <si>
+    <t>XCRPTOLV</t>
+  </si>
+  <si>
+    <t>LIVGASLOSS</t>
+  </si>
+  <si>
+    <t>XNLOSS</t>
+  </si>
+  <si>
+    <t>UNKMANURE</t>
+  </si>
+  <si>
+    <t>XUNK</t>
+  </si>
+  <si>
+    <t>IMANOT</t>
+  </si>
+  <si>
+    <t>XANOT</t>
+  </si>
+  <si>
+    <t>AN_LS_OTH</t>
+  </si>
+  <si>
+    <t>XANLSOT</t>
+  </si>
+  <si>
+    <t>LVSTCK_NOEDIBLE</t>
+  </si>
+  <si>
+    <t>XLVNOED</t>
+  </si>
+  <si>
+    <t>LIVESTOCK_EXPORTED</t>
+  </si>
+  <si>
+    <t>XLVSTEXP</t>
+  </si>
+  <si>
+    <t>LIVESTOCK_TO_HUMAN</t>
+  </si>
+  <si>
+    <t>XLVSTOHUM</t>
+  </si>
+  <si>
+    <t>IMPHMANA</t>
+  </si>
+  <si>
+    <t>XIMPHUMA</t>
+  </si>
+  <si>
+    <t>GRASS_TO_LIVESTOCK</t>
+  </si>
+  <si>
+    <t>XGRTOLV</t>
+  </si>
+  <si>
+    <t>WIDTH_MAX</t>
   </si>
 </sst>
 </file>
@@ -366,9 +357,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -406,7 +397,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -512,7 +503,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -654,7 +645,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -663,312 +654,312 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68CF53A0-BD45-4B99-9B03-00AA9F2C328A}">
   <dimension ref="A1:D26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="36.5" style="4" customWidth="1"/>
-    <col min="2" max="2" width="35.5" style="4" customWidth="1"/>
-    <col min="3" max="3" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.453125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="35.453125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="2" t="s">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="B11" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
+      <c r="D11" s="4"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="4"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>17</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D12" s="4"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="C13" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="4"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="4"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D13" s="4"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
+      <c r="D15" s="4"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="4"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="4" t="s">
+      <c r="C17" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D17" s="4"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D14" s="4"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D15" s="4"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
+      <c r="B18" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19" s="4"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="C21" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D16" s="4"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
+      <c r="B24" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B26" s="4" t="s">
         <v>22</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D17" s="4"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D19" s="4"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>45</v>
       </c>
       <c r="C26" s="4"/>
     </row>
